--- a/ch_11/ch_11_solution.xlsx
+++ b/ch_11/ch_11_solution.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30508"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_11_ai_assistance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4154512A-49CE-494D-BC02-B2CCFEFF735F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45614044-4574-4F08-BAAF-1856C3ECD594}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,11 +47,25 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="1">
+  <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="1"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
         </ext>
       </extLst>
     </bk>
@@ -61,9 +75,15 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="1">
+  <valueMetadata count="3">
     <bk>
       <rc t="2" v="0"/>
+    </bk>
+    <bk>
+      <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -113,6 +133,16 @@
     data=reg_df
 ).fit()
 model.summary2().tables[1]</code>
+    </pythonScript>
+    <pythonScript>
+      <code>mpg_df['horsepower'].corr(mpg_df['mpg'])</code>
+    </pythonScript>
+    <pythonScript>
+      <code>from scipy.stats import pearsonr, spearmanr
+hp = mpg_df.dropna(subset=['horsepower'])
+pearson = pearsonr(hp['horsepower'], hp['mpg'])[0]
+spearman = spearmanr(hp['horsepower'], hp['mpg'])[0]
+f"Pearson: {pearson:.2f}, Spearman: {spearman:.2f}"</code>
     </pythonScript>
   </pythonScripts>
 </python>
@@ -250,7 +280,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
   <rv s="0">
     <fb t="s">Rows in data: 398 / Rows used by model: 392</fb>
     <v>&lt;class 'str'&gt;</v>
@@ -259,16 +289,39 @@
     <v>Rows in data: 398 / Rows used by model: 392</v>
     <v>0</v>
   </rv>
+  <rv s="1">
+    <fb>-0.77842678389777564</fb>
+    <v>&lt;class 'numpy.float64'&gt;</v>
+    <v>float64</v>
+    <v>-0.7784267838977756</v>
+    <v>-0.77842678389777564</v>
+    <v>0</v>
+  </rv>
+  <rv s="0">
+    <fb t="s">Pearson: -0.78, Spearman: -0.85</fb>
+    <v>&lt;class 'str'&gt;</v>
+    <v>str</v>
+    <v>Pearson: -0.78, Spearman: -0.85</v>
+    <v>Pearson: -0.78, Spearman: -0.85</v>
+    <v>0</v>
+  </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
   <s t="_python">
     <k n="Python_type" t="s"/>
     <k n="Python_typeName" t="s"/>
     <k n="Python_str" t="s"/>
     <k n="basicValue" t="s"/>
+    <k n="_Provider" t="spb"/>
+  </s>
+  <s t="_python">
+    <k n="Python_type" t="s"/>
+    <k n="Python_typeName" t="s"/>
+    <k n="Python_str" t="s"/>
+    <k n="basicValue"/>
     <k n="_Provider" t="spb"/>
   </s>
 </rvStructures>
@@ -1464,6 +1517,10 @@
       <c r="H23" t="s">
         <v>10</v>
       </c>
+      <c r="J23" cm="1" vm="2">
+        <f t="array" ref="J23">_xlfn._xlws.PY(3,1)</f>
+        <v>-0.77842678389777564</v>
+      </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A24">
@@ -1515,6 +1572,10 @@
       </c>
       <c r="H25" t="s">
         <v>10</v>
+      </c>
+      <c r="J25" t="str" cm="1" vm="3">
+        <f t="array" ref="J25">_xlfn._xlws.PY(4,1)</f>
+        <v>Pearson: -0.78, Spearman: -0.85</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.45">
